--- a/600036_CMB/600036_CMB.xlsx
+++ b/600036_CMB/600036_CMB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\18803\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\PythonProject\A-share-Bank-Financial-Report-Analysis\600036_CMB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447DFE47-9FB4-409F-9D5D-4F696F54B737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F922DAF-E2B1-4409-A1FD-A4CB5804B6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6540" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="35">
   <si>
     <t>营业收入</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,10 +48,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每股现金流净额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>平均资产收益率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -160,18 +156,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>人民币流动性比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>外币流动性比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>流动性覆盖率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>正常类贷款迁徙率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -185,10 +169,6 @@
   </si>
   <si>
     <t>可疑类贷款迁徙率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>经现流</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -537,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -563,15 +543,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>451457</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
         <v>5.7</v>
@@ -579,289 +559,249 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>5.7</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>17.899999999999999</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>1.19</v>
+        <v>13070523</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>13.42</v>
+        <v>7258058</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>13070523</v>
+        <v>68206</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>7258058</v>
+        <v>267222</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>68206</v>
+        <v>11789624</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>267222</v>
+        <v>2761092</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>11789624</v>
+        <v>2579124</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>2761092</v>
+        <v>2234851</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>2579124</v>
+        <v>2261063</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>2234851</v>
+        <v>1272875</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>2261063</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>1272875</v>
+        <v>1375031</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>43.43</v>
+        <v>1067560</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1375031</v>
+        <v>7540202</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>1067560</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>7540202</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>1.78</v>
+        <v>63.87</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>1.87</v>
+        <v>36.130000000000003</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>63.87</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>36.130000000000003</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>31.98</v>
+        <v>391.79</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>0.94</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>391.79</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.6</v>
+        <v>16.510000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>14.16</v>
+        <v>18.239999999999998</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>16.510000000000002</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>18.239999999999998</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>60.62</v>
+        <v>72.510000000000005</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>125.78</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>220.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>28.66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>72.510000000000005</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>75.209999999999994</v>
       </c>
     </row>
@@ -873,7 +813,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95170128-8B75-4B3C-B904-1E83CD2631DB}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -898,305 +838,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>447023</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>5.66</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>5.65</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>17.72</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>1.28</v>
+        <v>12152036</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>14.45</v>
+        <v>6888315</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>12152036</v>
+        <v>65610</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>6888315</v>
+        <v>270301</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>65610</v>
+        <v>10918561</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>270301</v>
+        <v>2772365</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>10918561</v>
+        <v>2291188</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>2772365</v>
+        <v>1980251</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>2291188</v>
+        <v>2052783</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>1980251</v>
+        <v>1226014</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>2052783</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>1226014</v>
+        <v>1311742</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>41.46</v>
+        <v>1023048</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1311742</v>
+        <v>6885783</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>1023048</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>6885783</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>1.86</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>1.98</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>62.6</v>
+        <v>31.89</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>37.4</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>31.89</v>
+        <v>411.98</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>0.95</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>411.98</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.65</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>14.86</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>17.48</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>19.05</v>
+        <v>35.06</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>59.66</v>
+        <v>79.040000000000006</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>124.47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>227.29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>35.06</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>79.040000000000006</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>60.93</v>
       </c>
     </row>
@@ -1208,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85425F0F-59CE-4DB1-AEFB-6317792C8147}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -1233,305 +1133,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>357753</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>5.63</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>5.61</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>14.19</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>1.39</v>
+        <v>11028483</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>16.16</v>
+        <v>6508865</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>11028483</v>
+        <v>61579</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>6508865</v>
+        <v>269534</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>61579</v>
+        <v>9942754</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>269534</v>
+        <v>2644685</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>9942754</v>
+        <v>2015837</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>2644685</v>
+        <v>1829612</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>2015837</v>
+        <v>1665304</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>1829612</v>
+        <v>1076370</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>1665304</v>
+        <v>36.71</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>1076370</v>
+        <v>1181487</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>36.71</v>
+        <v>907308</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1181487</v>
+        <v>6608021</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>907308</v>
+        <v>2.0299999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>6608021</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>2.0299999999999998</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>2.15</v>
+        <v>36.700000000000003</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>63.3</v>
+        <v>32.96</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>36.700000000000003</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>32.96</v>
+        <v>437.7</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>0.95</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>437.7</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.74</v>
+        <v>16.010000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>13.73</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>16.010000000000002</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>17.88</v>
+        <v>34.950000000000003</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>56.24</v>
+        <v>74.09</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>95.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>198.01</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>34.950000000000003</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>74.09</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>55.33</v>
       </c>
     </row>
@@ -1543,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C7E03-EEF9-4665-8CD6-6DD93ACE52AD}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -1568,305 +1428,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>570143</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>5.25</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>22.61</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>1.42</v>
+        <v>10138912</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>6051459</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>10138912</v>
+        <v>58004</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>6051459</v>
+        <v>261476</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>58004</v>
+        <v>9184674</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>261476</v>
+        <v>2762671</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>9184674</v>
+        <v>1668882</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>2762671</v>
+        <v>1983364</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1668882</v>
+        <v>1120825</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>1983364</v>
+        <v>945503</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>1120825</v>
+        <v>32.71</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>945503</v>
+        <v>1037942</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>32.71</v>
+        <v>799352</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1037942</v>
+        <v>5841685</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>799352</v>
+        <v>2.2799999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>5841685</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>2.2799999999999998</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>2.4</v>
+        <v>36.700000000000003</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>63.3</v>
+        <v>32.880000000000003</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>36.700000000000003</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>32.880000000000003</v>
+        <v>450.79</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>450.79</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.78</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>13.68</v>
+        <v>17.77</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>15.75</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>17.77</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>51.94</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>74.31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>164.92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>27.25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>29.6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>19.72</v>
       </c>
     </row>
@@ -1878,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC5A80D1-36BE-41ED-8116-E82E59B3F5CA}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -1903,305 +1723,265 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>182048</v>
+        <v>4.6100000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>4.6100000000000003</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>4.59</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>7.22</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>1.36</v>
+        <v>9249021</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>16.89</v>
+        <v>5570034</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>9249021</v>
+        <v>50862</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>5570034</v>
+        <v>246104</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>50862</v>
+        <v>8383340</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>246104</v>
+        <v>2652817</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>8383340</v>
+        <v>1406107</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>2652817</v>
+        <v>1557861</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1406107</v>
+        <v>730293</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>1557861</v>
+        <v>858745</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>730293</v>
+        <v>29.01</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>858745</v>
+        <v>972606</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>29.01</v>
+        <v>704337</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>972606</v>
+        <v>5563724</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>704337</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>5563724</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>2.39</v>
+        <v>61.56</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>2.48</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>61.56</v>
+        <v>33.119999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>38.44</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>33.119999999999997</v>
+        <v>483.87</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>483.87</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.7</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>12.66</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>14.94</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>17.48</v>
+        <v>24.11</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>48.33</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>53.76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>164.82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>24.11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>36.1</v>
       </c>
     </row>
@@ -2213,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788DE462-357D-41E8-8E9A-DAF92235A9EE}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="2" customWidth="1"/>
@@ -2238,15 +2018,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>421328</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
         <v>3.79</v>
@@ -2254,289 +2034,249 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>3.79</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>16.71</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>1.23</v>
+        <v>8361448</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>15.7</v>
+        <v>5029128</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>8361448</v>
+        <v>53615</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>5029128</v>
+        <v>234664</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>53615</v>
+        <v>7631094</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>234664</v>
+        <v>2306134</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>7631094</v>
+        <v>1289556</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>2306134</v>
+        <v>1400520</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1289556</v>
+        <v>632126</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>1400520</v>
+        <v>723750</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>632126</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>723750</v>
+        <v>821290</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>25.36</v>
+        <v>610092</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>821290</v>
+        <v>4964542</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>610092</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>4964542</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>2.4</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>2.4900000000000002</v>
+        <v>36.299999999999997</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>63.7</v>
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>36.299999999999997</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3">
-        <v>33.299999999999997</v>
+        <v>437.68</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>1.07</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3">
-        <v>437.68</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>0.98</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>12.29</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>13.98</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3">
-        <v>16.54</v>
+        <v>38.119999999999997</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>42.06</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3">
-        <v>57.1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="3">
-        <v>145.91999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="3">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3">
-        <v>38.119999999999997</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3">
-        <v>82.37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3">
         <v>40.17</v>
       </c>
     </row>
